--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,14 +524,8 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>64</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -564,14 +558,8 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>174</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -604,14 +592,8 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -644,14 +626,8 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>16</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -684,14 +660,8 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>22</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -868,6 +838,206 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>64</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>174</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>22</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,14 +864,8 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>64</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -904,14 +898,8 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>174</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -944,14 +932,8 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>6</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -984,14 +966,8 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -1024,17 +1000,211 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>64</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>174</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>16</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>22</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>人工录入</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/集群设备清单表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,8 +524,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -558,8 +564,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>174</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -592,8 +604,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -626,8 +644,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -660,8 +684,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>22</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1034,14 +1064,8 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>64</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1074,14 +1098,8 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>174</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1114,14 +1132,8 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1154,14 +1166,8 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>16</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1194,17 +1200,181 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>22</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>人工录入</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
